--- a/Student_Results.xlsx
+++ b/Student_Results.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F59192E-8A09-D947-A269-52BD08B60A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03923B48-2660-C84D-BABD-E79A79DEA6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Student Results" sheetId="1" r:id="rId1"/>
+    <sheet name="قائمة الطلاب" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -28,43 +28,322 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+  <si>
+    <t>الرقم التسلسلي</t>
+  </si>
+  <si>
+    <t>Student_ID</t>
+  </si>
   <si>
     <t>Student_Name</t>
   </si>
   <si>
-    <t>Student_ID</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
     <t>أحمد محمد علي</t>
   </si>
   <si>
-    <t>Pass</t>
-  </si>
-  <si>
     <t>محمد عبدالله صالح</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
     <t>سارة أحمد محمد</t>
   </si>
   <si>
     <t>خالد علي حسن</t>
   </si>
   <si>
-    <t>فاطمة محمد أحمد</t>
+    <t>فاطمة صالح أحمد</t>
+  </si>
+  <si>
+    <t>علي يوسف سالم</t>
+  </si>
+  <si>
+    <t>مريم عبدالله حسن</t>
+  </si>
+  <si>
+    <t>إبراهيم محمد ناصر</t>
+  </si>
+  <si>
+    <t>نور أحمد محمود</t>
+  </si>
+  <si>
+    <t>عبدالله حسن علي</t>
+  </si>
+  <si>
+    <t>محمد صالح سالم</t>
+  </si>
+  <si>
+    <t>أحمد عبدالله محمد</t>
+  </si>
+  <si>
+    <t>خالد حسن صالح</t>
+  </si>
+  <si>
+    <t>سارة علي أحمد</t>
+  </si>
+  <si>
+    <t>فاطمة محمد حسن</t>
+  </si>
+  <si>
+    <t>علي عبدالله ناصر</t>
+  </si>
+  <si>
+    <t>مريم أحمد صالح</t>
+  </si>
+  <si>
+    <t>إبراهيم علي محمد</t>
+  </si>
+  <si>
+    <t>نور صالح أحمد</t>
+  </si>
+  <si>
+    <t>عبدالله محمد حسن</t>
+  </si>
+  <si>
+    <t>أحمد حسن سالم</t>
+  </si>
+  <si>
+    <t>محمد علي ناصر</t>
+  </si>
+  <si>
+    <t>سارة عبدالله صالح</t>
+  </si>
+  <si>
+    <t>خالد محمد أحمد</t>
+  </si>
+  <si>
+    <t>فاطمة حسن علي</t>
+  </si>
+  <si>
+    <t>علي صالح محمد</t>
+  </si>
+  <si>
+    <t>مريم عبدالله أحمد</t>
+  </si>
+  <si>
+    <t>إبراهيم حسن صالح</t>
+  </si>
+  <si>
+    <t>نور محمد سالم</t>
+  </si>
+  <si>
+    <t>عبدالله علي حسن</t>
+  </si>
+  <si>
+    <t>أحمد صالح ناصر</t>
+  </si>
+  <si>
+    <t>محمد حسن أحمد</t>
+  </si>
+  <si>
+    <t>سارة محمد علي</t>
+  </si>
+  <si>
+    <t>خالد عبدالله سالم</t>
+  </si>
+  <si>
+    <t>فاطمة علي صالح</t>
+  </si>
+  <si>
+    <t>علي محمد حسن</t>
+  </si>
+  <si>
+    <t>مريم صالح أحمد</t>
+  </si>
+  <si>
+    <t>إبراهيم عبدالله ناصر</t>
+  </si>
+  <si>
+    <t>نور حسن محمد</t>
+  </si>
+  <si>
+    <t>عبدالله صالح علي</t>
+  </si>
+  <si>
+    <t>أحمد علي سالم</t>
+  </si>
+  <si>
+    <t>محمد محمد حسن</t>
+  </si>
+  <si>
+    <t>سارة صالح أحمد</t>
+  </si>
+  <si>
+    <t>خالد حسن محمد</t>
+  </si>
+  <si>
+    <t>فاطمة عبدالله علي</t>
+  </si>
+  <si>
+    <t>علي حسن ناصر</t>
+  </si>
+  <si>
+    <t>مريم محمد صالح</t>
+  </si>
+  <si>
+    <t>إبراهيم صالح أحمد</t>
+  </si>
+  <si>
+    <t>نور عبدالله حسن</t>
+  </si>
+  <si>
+    <t>عبدالله محمد سالم</t>
+  </si>
+  <si>
+    <t>أحمد عبدالله ناصر</t>
+  </si>
+  <si>
+    <t>محمد صالح علي</t>
+  </si>
+  <si>
+    <t>سارة حسن محمد</t>
+  </si>
+  <si>
+    <t>خالد علي أحمد</t>
+  </si>
+  <si>
+    <t>فاطمة محمد صالح</t>
+  </si>
+  <si>
+    <t>علي عبدالله حسن</t>
+  </si>
+  <si>
+    <t>مريم أحمد علي</t>
+  </si>
+  <si>
+    <t>إبراهيم محمد سالم</t>
+  </si>
+  <si>
+    <t>نور صالح ناصر</t>
+  </si>
+  <si>
+    <t>عبدالله حسن أحمد</t>
+  </si>
+  <si>
+    <t>أحمد محمد حسن</t>
+  </si>
+  <si>
+    <t>محمد عبدالله علي</t>
+  </si>
+  <si>
+    <t>سارة علي صالح</t>
+  </si>
+  <si>
+    <t>خالد صالح محمد</t>
+  </si>
+  <si>
+    <t>فاطمة حسن أحمد</t>
+  </si>
+  <si>
+    <t>علي محمد ناصر</t>
+  </si>
+  <si>
+    <t>مريم عبدالله سالم</t>
+  </si>
+  <si>
+    <t>إبراهيم حسن علي</t>
+  </si>
+  <si>
+    <t>نور محمد صالح</t>
+  </si>
+  <si>
+    <t>عبدالله علي أحمد</t>
+  </si>
+  <si>
+    <t>أحمد صالح حسن</t>
+  </si>
+  <si>
+    <t>محمد حسن سالم</t>
+  </si>
+  <si>
+    <t>سارة محمد ناصر</t>
+  </si>
+  <si>
+    <t>خالد عبدالله علي</t>
+  </si>
+  <si>
+    <t>فاطمة علي محمد</t>
+  </si>
+  <si>
+    <t>علي صالح أحمد</t>
+  </si>
+  <si>
+    <t>مريم حسن صالح</t>
+  </si>
+  <si>
+    <t>إبراهيم عبدالله محمد</t>
+  </si>
+  <si>
+    <t>نور أحمد سالم</t>
+  </si>
+  <si>
+    <t>عبدالله محمد ناصر</t>
+  </si>
+  <si>
+    <t>أحمد حسن علي</t>
+  </si>
+  <si>
+    <t>محمد علي سالم</t>
+  </si>
+  <si>
+    <t>سارة عبدالله حسن</t>
+  </si>
+  <si>
+    <t>خالد محمد صالح</t>
+  </si>
+  <si>
+    <t>فاطمة صالح ناصر</t>
+  </si>
+  <si>
+    <t>علي حسن أحمد</t>
+  </si>
+  <si>
+    <t>مريم محمد علي</t>
+  </si>
+  <si>
+    <t>إبراهيم صالح حسن</t>
+  </si>
+  <si>
+    <t>نور عبدالله محمد</t>
+  </si>
+  <si>
+    <t>عبدالله أحمد سالم</t>
+  </si>
+  <si>
+    <t>أحمد علي ناصر</t>
+  </si>
+  <si>
+    <t>محمد صالح حسن</t>
+  </si>
+  <si>
+    <t>سارة حسن علي</t>
+  </si>
+  <si>
+    <t>خالد عبدالله أحمد</t>
+  </si>
+  <si>
+    <t>فاطمة محمد ناصر</t>
+  </si>
+  <si>
+    <t>علي عبدالله صالح</t>
+  </si>
+  <si>
+    <t>مريم أحمد حسن</t>
+  </si>
+  <si>
+    <t>إبراهيم محمد علي</t>
+  </si>
+  <si>
+    <t>نور صالح محمد</t>
+  </si>
+  <si>
+    <t>عبدالله حسن ناصر</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,20 +361,8 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF375623"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC65911"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -110,14 +377,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-        <bgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="FFF9FBFD"/>
+        <bgColor rgb="FFF9FBFD"/>
       </patternFill>
     </fill>
   </fills>
@@ -148,22 +409,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -467,11 +734,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.01953125" customWidth="1"/>
-    <col min="2" max="3" width="16.0078125" customWidth="1"/>
+    <col min="1" max="1" width="16.0078125" customWidth="1"/>
+    <col min="2" max="2" width="18.0234375" customWidth="1"/>
+    <col min="3" max="3" width="27.98046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -486,58 +754,1103 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
+      <c r="A2" s="2">
+        <v>1</v>
       </c>
       <c r="B2" s="3">
         <v>1001</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6">
+        <v>1002</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3">
-        <v>1002</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
+      <c r="A4" s="2">
+        <v>3</v>
       </c>
       <c r="B4" s="3">
         <v>1003</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="B5" s="6">
         <v>1004</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
+      <c r="A6" s="2">
+        <v>5</v>
       </c>
       <c r="B6" s="3">
         <v>1005</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1006</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1007</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1008</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1009</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1010</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1011</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6">
+        <v>1012</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1013</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6">
+        <v>1014</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1015</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6">
+        <v>1016</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1017</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6">
+        <v>1018</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1019</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6">
+        <v>1020</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1021</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6">
+        <v>1022</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1023</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6">
+        <v>1024</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1025</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6">
+        <v>1026</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3">
+        <v>1027</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6">
+        <v>1028</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1029</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6">
+        <v>1030</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1031</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6">
+        <v>1032</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3">
+        <v>1033</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6">
+        <v>1034</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3">
+        <v>1035</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="5">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6">
+        <v>1036</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3">
+        <v>1037</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="5">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6">
+        <v>1038</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3">
+        <v>1039</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="5">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6">
+        <v>1040</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3">
+        <v>1041</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="5">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6">
+        <v>1042</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3">
+        <v>1043</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="5">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6">
+        <v>1044</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3">
+        <v>1045</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="5">
+        <v>46</v>
+      </c>
+      <c r="B47" s="6">
+        <v>1046</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3">
+        <v>1047</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="5">
+        <v>48</v>
+      </c>
+      <c r="B49" s="6">
+        <v>1048</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3">
+        <v>1049</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="5">
+        <v>50</v>
+      </c>
+      <c r="B51" s="6">
+        <v>1050</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3">
+        <v>1051</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="5">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6">
+        <v>1052</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3">
+        <v>1053</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="5">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6">
+        <v>1054</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3">
+        <v>1055</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="5">
+        <v>56</v>
+      </c>
+      <c r="B57" s="6">
+        <v>1056</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3">
+        <v>1057</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="5">
+        <v>58</v>
+      </c>
+      <c r="B59" s="6">
+        <v>1058</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3">
+        <v>1059</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="5">
+        <v>60</v>
+      </c>
+      <c r="B61" s="6">
+        <v>1060</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3">
+        <v>1061</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="5">
+        <v>62</v>
+      </c>
+      <c r="B63" s="6">
+        <v>1062</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3">
+        <v>1063</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="5">
+        <v>64</v>
+      </c>
+      <c r="B65" s="6">
+        <v>1064</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3">
+        <v>1065</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="5">
+        <v>66</v>
+      </c>
+      <c r="B67" s="6">
+        <v>1066</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3">
+        <v>1067</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="5">
+        <v>68</v>
+      </c>
+      <c r="B69" s="6">
+        <v>1068</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3">
+        <v>1069</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="5">
+        <v>70</v>
+      </c>
+      <c r="B71" s="6">
+        <v>1070</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3">
+        <v>1071</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="5">
+        <v>72</v>
+      </c>
+      <c r="B73" s="6">
+        <v>1072</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3">
+        <v>1073</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="5">
+        <v>74</v>
+      </c>
+      <c r="B75" s="6">
+        <v>1074</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3">
+        <v>1075</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="5">
+        <v>76</v>
+      </c>
+      <c r="B77" s="6">
+        <v>1076</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3">
+        <v>1077</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="5">
+        <v>78</v>
+      </c>
+      <c r="B79" s="6">
+        <v>1078</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3">
+        <v>1079</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="5">
+        <v>80</v>
+      </c>
+      <c r="B81" s="6">
+        <v>1080</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3">
+        <v>1081</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="5">
+        <v>82</v>
+      </c>
+      <c r="B83" s="6">
+        <v>1082</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3">
+        <v>1083</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="5">
+        <v>84</v>
+      </c>
+      <c r="B85" s="6">
+        <v>1084</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3">
+        <v>1085</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" s="5">
+        <v>86</v>
+      </c>
+      <c r="B87" s="6">
+        <v>1086</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3">
+        <v>1087</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" s="5">
+        <v>88</v>
+      </c>
+      <c r="B89" s="6">
+        <v>1088</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3">
+        <v>1089</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="5">
+        <v>90</v>
+      </c>
+      <c r="B91" s="6">
+        <v>1090</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3">
+        <v>1091</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" s="5">
+        <v>92</v>
+      </c>
+      <c r="B93" s="6">
+        <v>1092</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3">
+        <v>1093</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" s="5">
+        <v>94</v>
+      </c>
+      <c r="B95" s="6">
+        <v>1094</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3">
+        <v>1095</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" s="5">
+        <v>96</v>
+      </c>
+      <c r="B97" s="6">
+        <v>1096</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" s="2">
+        <v>97</v>
+      </c>
+      <c r="B98" s="3">
+        <v>1097</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99" s="5">
+        <v>98</v>
+      </c>
+      <c r="B99" s="6">
+        <v>1098</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" s="2">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3">
+        <v>1099</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" s="5">
+        <v>100</v>
+      </c>
+      <c r="B101" s="6">
+        <v>1100</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
